--- a/resources/templates/standard/L1100-21.xlsx
+++ b/resources/templates/standard/L1100-21.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>설비 데이터 빽업 기준서</t>
   </si>
@@ -704,11 +707,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.15" customHeight="1" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -905,7 +910,7 @@
     </row>
     <row r="4" ht="20.15" customHeight="1" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -2029,7 +2034,7 @@
     </row>
     <row r="21" ht="20.15" customHeight="1" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -2097,18 +2102,18 @@
     </row>
     <row r="22" ht="20.15" customHeight="1" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
@@ -2118,18 +2123,18 @@
       <c r="N22" s="8"/>
       <c r="O22" s="8"/>
       <c r="P22" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q22" s="9"/>
       <c r="R22" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S22" s="8"/>
       <c r="T22" s="8"/>
       <c r="U22" s="8"/>
       <c r="V22" s="8"/>
       <c r="W22" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X22" s="8"/>
       <c r="Y22" s="8"/>
@@ -2670,7 +2675,7 @@
       <c r="AF30" s="3"/>
       <c r="AG30" s="3"/>
       <c r="AH30" s="15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI30" s="15"/>
       <c r="AJ30" s="15"/>
@@ -2969,7 +2974,7 @@
     </row>
     <row r="35" ht="20.15" customHeight="1" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="20"/>
@@ -3037,7 +3042,7 @@
     </row>
     <row r="36" ht="20.15" customHeight="1" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
@@ -3105,7 +3110,7 @@
     </row>
     <row r="37" ht="20.15" customHeight="1" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
@@ -3173,7 +3178,7 @@
     </row>
     <row r="38" ht="20.15" customHeight="1" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
@@ -3241,7 +3246,7 @@
     </row>
     <row r="39" ht="20.15" customHeight="1" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B39" s="22"/>
       <c r="C39" s="22"/>
